--- a/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="160">
   <si>
     <t>Mat</t>
   </si>
@@ -73,27 +73,78 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>COSCAHUA</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -106,30 +157,30 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
     <t>ARAGON</t>
   </si>
   <si>
@@ -148,9 +199,6 @@
     <t>COMIHUA</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
@@ -172,75 +220,105 @@
     <t>VEGA</t>
   </si>
   <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
     <t>TZOYONTLE</t>
   </si>
   <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
     <t>JACOBO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>SORIA</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
     <t>COXCAHUA</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>BRUNO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>CELESTINO</t>
   </si>
   <si>
     <t>ESTRADA</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>SIERRA</t>
   </si>
   <si>
@@ -259,27 +337,81 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
   </si>
   <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
     <t>JUAN DIEGO</t>
   </si>
   <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
     <t>JOSE DAMIAN</t>
   </si>
   <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
     <t>DULIAM</t>
   </si>
   <si>
@@ -289,33 +421,36 @@
     <t>OMAR</t>
   </si>
   <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
     <t>VICTOR ISRAEL</t>
   </si>
   <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
     <t>MIGUEL</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
     <t>JAFET</t>
   </si>
   <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
     <t>JONATHAN YOSEF</t>
   </si>
   <si>
@@ -334,9 +469,6 @@
     <t>ALEJANDRO GABRIEL</t>
   </si>
   <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
     <t>KARLA JIMENA</t>
   </si>
   <si>
@@ -344,9 +476,6 @@
   </si>
   <si>
     <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
   </si>
   <si>
     <t>MIA ARANZA</t>
@@ -1067,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,16 +1228,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1122,16 +1251,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1145,16 +1274,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920008</v>
+        <v>21330051920355</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1168,16 +1297,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920049</v>
+        <v>21330051920016</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1191,16 +1320,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920010</v>
+        <v>20330051920022</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1214,16 +1343,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920355</v>
+        <v>21330051920018</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1237,16 +1366,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920078</v>
+        <v>21330051920025</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1260,16 +1389,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920011</v>
+        <v>21330051920026</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1283,22 +1412,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920013</v>
+        <v>21330051920357</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1306,22 +1435,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920391</v>
+        <v>21330051920076</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1329,22 +1458,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920015</v>
+        <v>21330051920077</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1352,22 +1481,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920016</v>
+        <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1375,22 +1504,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920022</v>
+        <v>21330051920092</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1398,22 +1527,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920379</v>
+        <v>21330051920097</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1421,22 +1550,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920021</v>
+        <v>21330051920098</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1444,22 +1573,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920025</v>
+        <v>21330051920100</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1467,22 +1596,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920026</v>
+        <v>21330051920103</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1490,22 +1619,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920027</v>
+        <v>21330051920104</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1513,22 +1642,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920028</v>
+        <v>21330051920037</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1536,16 +1665,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920388</v>
+        <v>21330051920038</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1559,16 +1688,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920029</v>
+        <v>21330051920043</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1582,16 +1711,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920031</v>
+        <v>21330051920053</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1605,16 +1734,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920034</v>
+        <v>21330051920062</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1628,347 +1757,807 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920035</v>
+        <v>21330051920003</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920036</v>
+        <v>21330051920008</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920038</v>
+        <v>21330051920010</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920390</v>
+        <v>20330051920078</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920039</v>
+        <v>21330051920011</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920041</v>
+        <v>21330051920013</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920043</v>
+        <v>20330051920391</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920046</v>
+        <v>21330051920015</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920054</v>
+        <v>21330051920379</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920058</v>
+        <v>21330051920021</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920059</v>
+        <v>21330051920027</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920060</v>
+        <v>21330051920028</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920065</v>
+        <v>21330051920072</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920066</v>
+        <v>21330051920082</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
+        <v>20330051920302</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920096</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920099</v>
+      </c>
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" t="s">
+        <v>142</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920383</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920388</v>
+      </c>
+      <c r="B43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D43" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>21330051920029</v>
+      </c>
+      <c r="B44" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>21330051920031</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>21330051920034</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920035</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" t="s">
+        <v>148</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>21330051920036</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" t="s">
+        <v>88</v>
+      </c>
+      <c r="D48" t="s">
+        <v>149</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>21330051920390</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" t="s">
+        <v>150</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>21330051920039</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" t="s">
+        <v>151</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>21330051920041</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D51" t="s">
+        <v>152</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>21330051920046</v>
+      </c>
+      <c r="B52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>21330051920054</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" t="s">
+        <v>101</v>
+      </c>
+      <c r="D53" t="s">
+        <v>154</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>21330051920058</v>
+      </c>
+      <c r="B54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>21330051920059</v>
+      </c>
+      <c r="B55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>21330051920060</v>
+      </c>
+      <c r="B56" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" t="s">
+        <v>157</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>21330051920065</v>
+      </c>
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>21330051920066</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
         <v>21330051920067</v>
       </c>
-      <c r="B39" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" t="s">
-        <v>116</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" t="s">
+        <v>159</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
         <v>11</v>
       </c>
-      <c r="G39">
-        <v>2</v>
+      <c r="G59">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="151">
   <si>
     <t>Mat</t>
   </si>
@@ -127,24 +127,18 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -175,138 +169,129 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>BRUNO</t>
   </si>
   <si>
@@ -334,9 +319,6 @@
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
@@ -391,36 +373,30 @@
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>OMAR</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
     <t>VICTOR ISRAEL</t>
   </si>
   <si>
@@ -440,9 +416,6 @@
   </si>
   <si>
     <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>JAIME</t>
   </si>
   <si>
     <t>LUIS REY</t>
@@ -923,19 +896,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>45.95</v>
+        <v>48.65</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -949,19 +922,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="H4">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +1013,7 @@
         <v>37</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1063,7 +1036,7 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1148,19 +1121,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>45.95</v>
+        <v>48.65</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1174,19 +1147,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="H4">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1237,7 +1210,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1257,10 +1230,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1280,10 +1253,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1303,10 +1276,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1326,10 +1299,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1349,10 +1322,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1372,10 +1345,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1395,10 +1368,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1418,10 +1391,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1444,7 +1417,7 @@
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1464,10 +1437,10 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1487,10 +1460,10 @@
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1510,10 +1483,10 @@
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1533,10 +1506,10 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1556,10 +1529,10 @@
         <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1579,10 +1552,10 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1602,10 +1575,10 @@
         <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1625,10 +1598,10 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1648,10 +1621,10 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1665,16 +1638,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920038</v>
+        <v>21330051920062</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1688,85 +1661,85 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920043</v>
+        <v>21330051920003</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920053</v>
+        <v>21330051920008</v>
       </c>
       <c r="B23" t="s">
         <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920062</v>
+        <v>21330051920010</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920003</v>
+        <v>20330051920078</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1780,16 +1753,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920008</v>
+        <v>21330051920011</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1803,16 +1776,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920010</v>
+        <v>21330051920013</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1826,16 +1799,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920078</v>
+        <v>20330051920391</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1849,16 +1822,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920011</v>
+        <v>21330051920015</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1872,16 +1845,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920013</v>
+        <v>21330051920379</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1895,16 +1868,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920391</v>
+        <v>21330051920021</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -1918,16 +1891,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920015</v>
+        <v>21330051920027</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -1941,16 +1914,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920379</v>
+        <v>21330051920028</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -1964,22 +1937,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920021</v>
+        <v>21330051920072</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1987,22 +1960,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920027</v>
+        <v>21330051920082</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2010,22 +1983,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920028</v>
+        <v>20330051920302</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2033,16 +2006,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920072</v>
+        <v>21330051920099</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2056,16 +2029,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920082</v>
+        <v>21330051920383</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2079,22 +2052,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920302</v>
+        <v>21330051920388</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2102,22 +2075,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>21330051920096</v>
+        <v>21330051920029</v>
       </c>
       <c r="B40" t="s">
         <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2125,22 +2098,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>21330051920099</v>
+        <v>21330051920031</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2148,22 +2121,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>21330051920383</v>
+        <v>21330051920034</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2171,16 +2144,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>21330051920388</v>
+        <v>21330051920035</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2194,16 +2167,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>21330051920029</v>
+        <v>21330051920036</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2217,16 +2190,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>21330051920031</v>
+        <v>21330051920390</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2240,16 +2213,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>21330051920034</v>
+        <v>21330051920039</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2263,16 +2236,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>21330051920035</v>
+        <v>21330051920041</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2286,16 +2259,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>21330051920036</v>
+        <v>21330051920046</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D48" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2309,16 +2282,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>21330051920390</v>
+        <v>21330051920054</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2332,16 +2305,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>21330051920039</v>
+        <v>21330051920058</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2355,16 +2328,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>21330051920041</v>
+        <v>21330051920059</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2378,16 +2351,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>21330051920046</v>
+        <v>21330051920060</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D52" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2401,16 +2374,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>21330051920054</v>
+        <v>21330051920065</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2424,16 +2397,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>21330051920058</v>
+        <v>21330051920067</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2442,121 +2415,6 @@
         <v>11</v>
       </c>
       <c r="G54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>21330051920059</v>
-      </c>
-      <c r="B55" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" t="s">
-        <v>102</v>
-      </c>
-      <c r="D55" t="s">
-        <v>156</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>21330051920060</v>
-      </c>
-      <c r="B56" t="s">
-        <v>64</v>
-      </c>
-      <c r="C56" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" t="s">
-        <v>157</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>11</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>21330051920065</v>
-      </c>
-      <c r="B57" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" t="s">
-        <v>158</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>21330051920066</v>
-      </c>
-      <c r="B58" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" t="s">
-        <v>105</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>21330051920067</v>
-      </c>
-      <c r="B59" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" t="s">
-        <v>32</v>
-      </c>
-      <c r="D59" t="s">
-        <v>159</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>11</v>
-      </c>
-      <c r="G59">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="89">
   <si>
     <t>Mat</t>
   </si>
@@ -76,397 +76,211 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MACIEL</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MIXCOA</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CABALLERO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>LEPE</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
     <t>MARIA VALERIA</t>
   </si>
   <si>
-    <t>DAVID DANIEL</t>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
   </si>
   <si>
     <t>JOSE EDUARDO</t>
   </si>
   <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>YARED</t>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
   </si>
   <si>
     <t>HANIA ZARETH</t>
@@ -870,19 +684,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -896,19 +710,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>48.65</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -922,19 +736,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>34.15</v>
+        <v>53.66</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -987,16 +801,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>38.89</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1010,16 +827,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>64.86</v>
+      </c>
+      <c r="H3">
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1033,16 +853,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>41.46</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -1095,19 +918,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1121,19 +944,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>48.65</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1147,19 +970,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>34.15</v>
+        <v>53.66</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1207,10 +1030,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1224,16 +1047,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920049</v>
+        <v>21330051920355</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1247,16 +1070,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920355</v>
+        <v>21330051920028</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1270,22 +1093,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920016</v>
+        <v>21330051920072</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1293,22 +1116,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920022</v>
+        <v>21330051920357</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1316,22 +1139,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920018</v>
+        <v>21330051920082</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1339,22 +1162,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920025</v>
+        <v>21330051920098</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1362,22 +1185,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920026</v>
+        <v>21330051920100</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1385,22 +1208,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920357</v>
+        <v>21330051920037</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1408,22 +1231,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920076</v>
+        <v>21330051920041</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1431,154 +1254,154 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920077</v>
+        <v>21330051920003</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920080</v>
+        <v>21330051920010</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920092</v>
+        <v>21330051920013</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920097</v>
+        <v>21330051920015</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920098</v>
+        <v>20330051920022</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920100</v>
+        <v>21330051920021</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920103</v>
+        <v>21330051920077</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1587,21 +1410,21 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920104</v>
+        <v>21330051920383</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1610,21 +1433,21 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920037</v>
+        <v>21330051920388</v>
       </c>
       <c r="B20" t="s">
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1633,21 +1456,21 @@
         <v>11</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920062</v>
+        <v>21330051920029</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1656,27 +1479,27 @@
         <v>11</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920003</v>
+        <v>21330051920036</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1684,22 +1507,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920008</v>
+        <v>21330051920039</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1707,22 +1530,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920010</v>
+        <v>21330051920046</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1730,22 +1553,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920078</v>
+        <v>21330051920054</v>
       </c>
       <c r="B25" t="s">
         <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1753,22 +1576,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920011</v>
+        <v>21330051920058</v>
       </c>
       <c r="B26" t="s">
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1776,22 +1599,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920013</v>
+        <v>21330051920062</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1799,622 +1622,24 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920391</v>
+        <v>21330051920067</v>
       </c>
       <c r="B28" t="s">
         <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920015</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920379</v>
-      </c>
-      <c r="B30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>127</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920021</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920027</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920028</v>
-      </c>
-      <c r="B33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" t="s">
-        <v>129</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920072</v>
-      </c>
-      <c r="B34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" t="s">
-        <v>130</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920082</v>
-      </c>
-      <c r="B35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920302</v>
-      </c>
-      <c r="B36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920099</v>
-      </c>
-      <c r="B37" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920383</v>
-      </c>
-      <c r="B38" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" t="s">
-        <v>134</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920388</v>
-      </c>
-      <c r="B39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" t="s">
-        <v>135</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920029</v>
-      </c>
-      <c r="B40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" t="s">
-        <v>136</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920031</v>
-      </c>
-      <c r="B41" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>11</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920034</v>
-      </c>
-      <c r="B42" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42" t="s">
-        <v>138</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920035</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" t="s">
-        <v>139</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>11</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920036</v>
-      </c>
-      <c r="B44" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" t="s">
-        <v>140</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920390</v>
-      </c>
-      <c r="B45" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>11</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920039</v>
-      </c>
-      <c r="B46" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" t="s">
-        <v>142</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920041</v>
-      </c>
-      <c r="B47" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" t="s">
-        <v>143</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920046</v>
-      </c>
-      <c r="B48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" t="s">
-        <v>95</v>
-      </c>
-      <c r="D48" t="s">
-        <v>144</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>21330051920054</v>
-      </c>
-      <c r="B49" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" t="s">
-        <v>96</v>
-      </c>
-      <c r="D49" t="s">
-        <v>145</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>21330051920058</v>
-      </c>
-      <c r="B50" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" t="s">
-        <v>146</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>21330051920059</v>
-      </c>
-      <c r="B51" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" t="s">
-        <v>147</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>21330051920060</v>
-      </c>
-      <c r="B52" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" t="s">
-        <v>148</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>11</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>21330051920065</v>
-      </c>
-      <c r="B53" t="s">
-        <v>62</v>
-      </c>
-      <c r="C53" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" t="s">
-        <v>149</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>11</v>
-      </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>21330051920067</v>
-      </c>
-      <c r="B54" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" t="s">
-        <v>150</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="86">
   <si>
     <t>Mat</t>
   </si>
@@ -133,9 +133,6 @@
     <t>COMIHUA</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -196,9 +193,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
     <t>LEPE</t>
   </si>
   <si>
@@ -269,9 +263,6 @@
   </si>
   <si>
     <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
   </si>
   <si>
     <t>ANGEL GABRIEL</t>
@@ -736,19 +727,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>53.66</v>
+        <v>56.1</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -853,16 +844,16 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>41.46</v>
+        <v>46.34</v>
       </c>
       <c r="H4">
         <v>8.6</v>
@@ -970,16 +961,16 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>53.66</v>
+        <v>56.1</v>
       </c>
       <c r="H4">
         <v>8.699999999999999</v>
@@ -992,7 +983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1033,7 +1024,7 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1053,10 +1044,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1076,10 +1067,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1099,10 +1090,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1122,10 +1113,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1145,10 +1136,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1171,7 +1162,7 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1191,10 +1182,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1214,10 +1205,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1237,10 +1228,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1260,10 +1251,10 @@
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1283,10 +1274,10 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1309,7 +1300,7 @@
         <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1332,7 +1323,7 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1352,10 +1343,10 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1375,10 +1366,10 @@
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1398,10 +1389,10 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1421,10 +1412,10 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1444,10 +1435,10 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1467,10 +1458,10 @@
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1490,10 +1481,10 @@
         <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1513,10 +1504,10 @@
         <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1530,16 +1521,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920046</v>
+        <v>21330051920054</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1553,16 +1544,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920054</v>
+        <v>21330051920058</v>
       </c>
       <c r="B25" t="s">
         <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1576,16 +1567,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920058</v>
+        <v>21330051920062</v>
       </c>
       <c r="B26" t="s">
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1599,16 +1590,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1617,29 +1608,6 @@
         <v>11</v>
       </c>
       <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920067</v>
-      </c>
-      <c r="B28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="109">
   <si>
     <t>Mat</t>
   </si>
@@ -73,88 +73,157 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>URBINA</t>
+  </si>
+  <si>
     <t>CHACÓN</t>
   </si>
   <si>
-    <t>CABALLERO</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>VEGA</t>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MORA</t>
   </si>
   <si>
     <t>GASPAR</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
   </si>
   <si>
     <t>BRETON</t>
@@ -163,34 +232,10 @@
     <t>MORENO</t>
   </si>
   <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>VERA</t>
   </si>
   <si>
     <t>LEPE</t>
@@ -199,70 +244,94 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
     <t>MARIA VALERIA</t>
   </si>
   <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
     <t>JAFET</t>
   </si>
   <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
     <t>KATHIA</t>
   </si>
   <si>
-    <t>LUIS ARMANDO</t>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>VANESSA AMAIRANY</t>
   </si>
   <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
     <t>KIMBERLY</t>
   </si>
   <si>
-    <t>JONATHAN YOSEF</t>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>MARISOL</t>
   </si>
   <si>
     <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
   </si>
   <si>
     <t>ANGEL GABRIEL</t>
@@ -727,19 +796,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>56.1</v>
+        <v>60.98</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -818,19 +887,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>64.86</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -844,19 +913,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>46.34</v>
+        <v>56.1</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -947,7 +1016,7 @@
         <v>75.68000000000001</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -961,19 +1030,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>56.1</v>
+        <v>60.98</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1015,16 +1084,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>21330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1038,16 +1107,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920355</v>
+        <v>21330051920007</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1061,16 +1130,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920028</v>
+        <v>20330051920019</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1084,22 +1153,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920072</v>
+        <v>21330051920026</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1113,10 +1182,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1130,16 +1199,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920082</v>
+        <v>21330051920098</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1153,16 +1222,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920098</v>
+        <v>21330051920107</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1176,22 +1245,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920100</v>
+        <v>21330051920388</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1205,10 +1274,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1222,16 +1291,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920041</v>
+        <v>21330051920039</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1245,16 +1314,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920003</v>
+        <v>21330051920001</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1268,16 +1337,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920010</v>
+        <v>21330051920003</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1291,16 +1360,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920013</v>
+        <v>21330051920005</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1314,16 +1383,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920015</v>
+        <v>21330051920010</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1337,16 +1406,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920022</v>
+        <v>21330051920355</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1360,16 +1429,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920021</v>
+        <v>21330051920013</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1383,22 +1452,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920077</v>
+        <v>21330051920015</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
         <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1406,22 +1475,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920383</v>
+        <v>20330051920022</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1429,22 +1498,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920388</v>
+        <v>21330051920385</v>
       </c>
       <c r="B20" t="s">
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1452,22 +1521,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920029</v>
+        <v>21330051920021</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1475,22 +1544,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920036</v>
+        <v>21330051920023</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1498,22 +1567,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920039</v>
+        <v>21330051920028</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1521,22 +1590,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920054</v>
+        <v>21330051920393</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1544,22 +1613,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920058</v>
+        <v>21330051920072</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1567,22 +1636,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920062</v>
+        <v>21330051920077</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1590,24 +1659,231 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920067</v>
+        <v>21330051920082</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920383</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920109</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920029</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
         <v>11</v>
       </c>
-      <c r="G27">
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920036</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051920054</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920058</v>
+      </c>
+      <c r="B34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920062</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920067</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="72">
   <si>
     <t>Mat</t>
   </si>
@@ -91,159 +91,93 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>TENTZOHUA</t>
   </si>
   <si>
-    <t>ARAGON</t>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>LEPE</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>EDGAR FLORENCIO</t>
   </si>
   <si>
@@ -262,85 +196,40 @@
     <t>ALDO GEOVANNI</t>
   </si>
   <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
     <t>RUBI</t>
   </si>
   <si>
-    <t>JONATHAN YOSEF</t>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
+    <t>NUBIA NAHOMI</t>
   </si>
   <si>
     <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
   </si>
   <si>
     <t>HANIA ZARETH</t>
@@ -744,19 +633,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -770,19 +659,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>75.68000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -796,19 +685,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>60.98</v>
+        <v>73.17</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -861,19 +750,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -887,19 +776,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>67.56999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -913,19 +802,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>56.1</v>
+        <v>73.17</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -978,19 +867,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1004,19 +893,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>75.68000000000001</v>
+        <v>81.08</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1030,19 +919,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>60.98</v>
+        <v>70.73</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1052,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1090,10 +979,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1113,10 +1002,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1136,10 +1025,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1159,10 +1048,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1182,10 +1071,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1205,10 +1094,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1222,22 +1111,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920107</v>
+        <v>21330051920032</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1245,85 +1134,85 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920388</v>
+        <v>21330051920003</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920037</v>
+        <v>21330051920385</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920039</v>
+        <v>21330051920021</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920001</v>
+        <v>21330051920028</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1337,22 +1226,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920003</v>
+        <v>21330051920072</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1360,22 +1249,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920005</v>
+        <v>21330051920082</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1383,22 +1272,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920010</v>
+        <v>21330051920085</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1406,22 +1295,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920355</v>
+        <v>21330051920107</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1429,22 +1318,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920013</v>
+        <v>21330051920109</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1452,22 +1341,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920015</v>
+        <v>21330051920037</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1475,22 +1364,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920022</v>
+        <v>21330051920047</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1498,22 +1387,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920385</v>
+        <v>21330051920054</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1521,369 +1410,24 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920021</v>
+        <v>21330051920067</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920023</v>
-      </c>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920028</v>
-      </c>
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>95</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920393</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920072</v>
-      </c>
-      <c r="B25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920077</v>
-      </c>
-      <c r="B26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920082</v>
-      </c>
-      <c r="B27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920100</v>
-      </c>
-      <c r="B28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920383</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920109</v>
-      </c>
-      <c r="B30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920029</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920036</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920054</v>
-      </c>
-      <c r="B33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920058</v>
-      </c>
-      <c r="B34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920062</v>
-      </c>
-      <c r="B35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920067</v>
-      </c>
-      <c r="B36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36">
         <v>1</v>
       </c>
     </row>
